--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="132">
   <si>
     <t>Data</t>
   </si>
@@ -3529,14 +3529,30 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76">
+      <c r="A76" s="4">
+        <v>46273</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D76" s="3">
+        <v>1</v>
+      </c>
+      <c r="E76" s="3">
+        <v>396</v>
+      </c>
+      <c r="F76" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>396</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="134">
   <si>
     <t>Data</t>
   </si>
@@ -416,7 +416,13 @@
     <t>dra Karin</t>
   </si>
   <si>
-    <t>$189,81</t>
+    <t>$114,79</t>
+  </si>
+  <si>
+    <t>$119,92</t>
+  </si>
+  <si>
+    <t>$179,82</t>
   </si>
 </sst>
 </file>
@@ -801,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -849,8 +855,8 @@
       <c r="D2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
+      <c r="E2" s="3">
+        <v>89.91</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>23</v>
@@ -876,8 +882,8 @@
       <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
+      <c r="E3" s="3">
+        <v>89.91</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>23</v>
@@ -903,8 +909,8 @@
       <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>29</v>
+      <c r="E4" s="3">
+        <v>98.91</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>23</v>
@@ -930,8 +936,8 @@
       <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>33</v>
+      <c r="E5" s="3">
+        <v>38.25</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>23</v>
@@ -953,8 +959,8 @@
       <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>36</v>
+      <c r="E6" s="3">
+        <v>33.56</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>37</v>
@@ -976,8 +982,8 @@
       <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>41</v>
+      <c r="E7" s="3">
+        <v>20.7</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>23</v>
@@ -999,8 +1005,8 @@
       <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
+      <c r="E8" s="3">
+        <v>89.91</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>23</v>
@@ -1022,8 +1028,8 @@
       <c r="D9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>20</v>
+      <c r="E9" s="3">
+        <v>89.91</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>23</v>
@@ -1045,8 +1051,8 @@
       <c r="D10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
+      <c r="E10" s="3">
+        <v>89.91</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>23</v>
@@ -1068,8 +1074,8 @@
       <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>20</v>
+      <c r="E11" s="3">
+        <v>89.91</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>23</v>
@@ -1091,8 +1097,8 @@
       <c r="D12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
+      <c r="E12" s="3">
+        <v>89.91</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>23</v>
@@ -1114,8 +1120,8 @@
       <c r="D13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>62</v>
+      <c r="E13" s="3">
+        <v>513</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>23</v>
@@ -1137,8 +1143,8 @@
       <c r="D14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>69</v>
+      <c r="E14" s="3">
+        <v>170.9</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>23</v>
@@ -1160,8 +1166,8 @@
       <c r="D15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>73</v>
+      <c r="E15" s="3">
+        <v>69.89</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>23</v>
@@ -1183,8 +1189,8 @@
       <c r="D16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>76</v>
+      <c r="E16" s="3">
+        <v>78.5</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>23</v>
@@ -1206,8 +1212,8 @@
       <c r="D17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>86</v>
+      <c r="E17" s="3">
+        <v>30</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>23</v>
@@ -1229,8 +1235,8 @@
       <c r="D18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>89</v>
+      <c r="E18" s="3">
+        <v>42.99</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>23</v>
@@ -1252,8 +1258,8 @@
       <c r="D19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>98</v>
+      <c r="E19" s="3">
+        <v>415.1</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>23</v>
@@ -1275,8 +1281,8 @@
       <c r="D20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>100</v>
+      <c r="E20" s="3">
+        <v>95</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>23</v>
@@ -1298,8 +1304,8 @@
       <c r="D21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>101</v>
+      <c r="E21" s="3">
+        <v>359.64</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>23</v>
@@ -1321,8 +1327,8 @@
       <c r="D22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>108</v>
+      <c r="E22" s="3">
+        <v>290.99</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>23</v>
@@ -1344,8 +1350,8 @@
       <c r="D23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>114</v>
+      <c r="E23" s="3">
+        <v>50</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>23</v>
@@ -1367,8 +1373,8 @@
       <c r="D24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>113</v>
+      <c r="E24" s="3">
+        <v>79.7</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>23</v>
@@ -1390,8 +1396,8 @@
       <c r="D25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>116</v>
+      <c r="E25" s="3">
+        <v>92.05</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>23</v>
@@ -1414,8 +1420,8 @@
       <c r="D26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>122</v>
+      <c r="E26" s="3">
+        <v>99.46</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>23</v>
@@ -1437,8 +1443,8 @@
       <c r="D27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>126</v>
+      <c r="E27" s="3">
+        <v>197.8</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>23</v>
@@ -1460,8 +1466,8 @@
       <c r="D28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>128</v>
+      <c r="E28" s="3">
+        <v>269.73</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>23</v>
@@ -1483,13 +1489,82 @@
       <c r="D29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>131</v>
+      <c r="E29" s="3">
+        <v>189.81</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="3">
+        <v>119.92</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>46275</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="3">
+        <v>114.79</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>46275</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="3">
+        <v>179.82</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9152,7 +9227,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -9744,16 +9819,64 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="A30" s="4">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="A31" s="4">
+        <v>46275</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>46275</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="138">
   <si>
     <t>Data</t>
   </si>
@@ -423,6 +423,18 @@
   </si>
   <si>
     <t>$179,82</t>
+  </si>
+  <si>
+    <t>BONE PERSONALIZADO</t>
+  </si>
+  <si>
+    <t>MARKETING</t>
+  </si>
+  <si>
+    <t>$99,80</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -807,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1567,6 +1579,1172 @@
       <c r="G32" s="3" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9227,7 +10405,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -9878,6 +11056,26 @@
         <v>23</v>
       </c>
     </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="139">
   <si>
     <t>Data</t>
   </si>
@@ -435,6 +435,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>CHAV./ TAMPAO</t>
   </si>
 </sst>
 </file>
@@ -4809,14 +4812,30 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77">
+      <c r="A77" s="4">
+        <v>46286</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1</v>
+      </c>
+      <c r="E77" s="3">
+        <v>292</v>
+      </c>
+      <c r="F77" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>292</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="141">
   <si>
     <t>Data</t>
   </si>
@@ -438,6 +438,12 @@
   </si>
   <si>
     <t>CHAV./ TAMPAO</t>
+  </si>
+  <si>
+    <t>Zenita</t>
+  </si>
+  <si>
+    <t>QR PIX</t>
   </si>
 </sst>
 </file>
@@ -4839,14 +4845,29 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="A78" s="4">
+        <v>46287</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D78" s="3">
+        <v>1</v>
+      </c>
+      <c r="E78" s="3">
+        <v>1</v>
+      </c>
+      <c r="F78" s="3">
+        <v>35</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="143">
   <si>
     <t>Data</t>
   </si>
@@ -444,6 +444,12 @@
   </si>
   <si>
     <t>QR PIX</t>
+  </si>
+  <si>
+    <t>GIGI</t>
+  </si>
+  <si>
+    <t>CHAVEIRO</t>
   </si>
 </sst>
 </file>
@@ -4871,14 +4877,30 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79">
+      <c r="A79" s="4">
+        <v>46287</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D79" s="3">
+        <v>2</v>
+      </c>
+      <c r="E79" s="3">
+        <v>6</v>
+      </c>
+      <c r="F79" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="146">
   <si>
     <t>Data</t>
   </si>
@@ -450,6 +450,15 @@
   </si>
   <si>
     <t>CHAVEIRO</t>
+  </si>
+  <si>
+    <t>Diandra</t>
+  </si>
+  <si>
+    <t>Fran Marcelo</t>
+  </si>
+  <si>
+    <t>mini Jesus</t>
   </si>
 </sst>
 </file>
@@ -4904,28 +4913,60 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80">
+      <c r="A80" s="4">
+        <v>46294</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D80" s="3">
+        <v>1</v>
+      </c>
+      <c r="E80" s="3">
+        <v>20</v>
+      </c>
+      <c r="F80" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81">
+        <v>20</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>46294</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D81" s="3">
+        <v>1</v>
+      </c>
+      <c r="E81" s="3">
+        <v>15</v>
+      </c>
+      <c r="F81" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -4936,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -4947,7 +4988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -4958,73 +4999,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F85">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F86">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F88">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F91">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F92">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F93">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F94">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F95">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F96">
         <f t="shared" si="2"/>
         <v>0</v>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="148">
   <si>
     <t>Data</t>
   </si>
@@ -459,6 +459,12 @@
   </si>
   <si>
     <t>mini Jesus</t>
+  </si>
+  <si>
+    <t>Ferriforte</t>
+  </si>
+  <si>
+    <t>chaveiro</t>
   </si>
 </sst>
 </file>
@@ -4967,14 +4973,30 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82">
+      <c r="A82" s="4">
+        <v>46295</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D82" s="3">
+        <v>10</v>
+      </c>
+      <c r="E82" s="3">
+        <v>10</v>
+      </c>
+      <c r="F82" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="149">
   <si>
     <t>Data</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>chaveiro</t>
+  </si>
+  <si>
+    <t>Chav.Personalizado</t>
   </si>
 </sst>
 </file>
@@ -5000,25 +5003,57 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83">
+      <c r="A83" s="4">
+        <v>46298</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D83" s="3">
+        <v>42</v>
+      </c>
+      <c r="E83" s="3">
+        <v>6</v>
+      </c>
+      <c r="F83" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>252</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84">
+      <c r="A84" s="4">
+        <v>46298</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D84" s="3">
+        <v>4</v>
+      </c>
+      <c r="E84" s="3">
+        <v>18</v>
+      </c>
+      <c r="F84" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="149">
   <si>
     <t>Data</t>
   </si>
@@ -5057,168 +5057,245 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F85">
+      <c r="A85" s="4">
+        <v>46308</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D85" s="3">
+        <v>48</v>
+      </c>
+      <c r="E85" s="3">
+        <v>6</v>
+      </c>
+      <c r="F85" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>288</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F86">
+      <c r="A86" s="4">
+        <v>46308</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D86" s="3">
+        <v>8</v>
+      </c>
+      <c r="E86" s="3">
+        <v>18</v>
+      </c>
+      <c r="F86" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F87">
+      <c r="A87" s="4">
+        <v>46311</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D87" s="3">
+        <v>2</v>
+      </c>
+      <c r="E87" s="3">
+        <v>10</v>
+      </c>
+      <c r="F87" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="3"/>
       <c r="F88">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
       <c r="F89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="3"/>
       <c r="F90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
       <c r="F91">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="3"/>
       <c r="F92">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="3"/>
       <c r="F93">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="3"/>
       <c r="F94">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="3"/>
       <c r="F95">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="3"/>
       <c r="F96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="3"/>
       <c r="F97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="3"/>
       <c r="F98">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="3"/>
       <c r="F99">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="3"/>
       <c r="F100">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="3"/>
       <c r="F101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F102">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F103">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F105">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F108">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F109">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F110">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F112">
         <f t="shared" si="2"/>
         <v>0</v>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,23 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
-    <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
-    <sheet name="Vendas" sheetId="2" r:id="rId2"/>
-    <sheet name="Gastos" sheetId="3" r:id="rId3"/>
+    <sheet name="Vendas" sheetId="2" r:id="rId1"/>
+    <sheet name="Gastos" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="140">
   <si>
     <t>Data</t>
   </si>
@@ -29,9 +28,6 @@
     <t>Descrição</t>
   </si>
   <si>
-    <t>Tipo (Gasto/Venda)</t>
-  </si>
-  <si>
     <t>Categoria</t>
   </si>
   <si>
@@ -44,18 +40,6 @@
     <t>Observações</t>
   </si>
   <si>
-    <t>Resumo</t>
-  </si>
-  <si>
-    <t>Total Vendas</t>
-  </si>
-  <si>
-    <t>Total Gastos</t>
-  </si>
-  <si>
-    <t>Lucro</t>
-  </si>
-  <si>
     <t>Cliente</t>
   </si>
   <si>
@@ -89,9 +73,6 @@
     <t>Insumos</t>
   </si>
   <si>
-    <t>Gasto</t>
-  </si>
-  <si>
     <t>PIX</t>
   </si>
   <si>
@@ -170,9 +151,6 @@
     <t>Filamento Nude</t>
   </si>
   <si>
-    <t>CONEXÃO</t>
-  </si>
-  <si>
     <t>Filamento Amarelo</t>
   </si>
   <si>
@@ -206,9 +184,6 @@
     <t>CHAVEIRO DEMONG</t>
   </si>
   <si>
-    <t>FILAMENTOS 3D PRIME</t>
-  </si>
-  <si>
     <t>$513,00</t>
   </si>
   <si>
@@ -368,9 +343,6 @@
     <t>$50,00</t>
   </si>
   <si>
-    <t>Filamento PLA Branco</t>
-  </si>
-  <si>
     <t>$92,05</t>
   </si>
   <si>
@@ -395,9 +367,6 @@
     <t>FILAMENTO PRETO - CREALITY</t>
   </si>
   <si>
-    <t>FILAMENTO PRETO CREALITY</t>
-  </si>
-  <si>
     <t>TAMPÃO PERSONALIZADO</t>
   </si>
   <si>
@@ -434,9 +403,6 @@
     <t>$99,80</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>CHAV./ TAMPAO</t>
   </si>
   <si>
@@ -468,6 +434,12 @@
   </si>
   <si>
     <t>Chav.Personalizado</t>
+  </si>
+  <si>
+    <t>FILAMENTO PRETO</t>
+  </si>
+  <si>
+    <t>$176,34</t>
   </si>
 </sst>
 </file>
@@ -503,7 +475,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -511,26 +483,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -545,8 +502,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -852,1940 +807,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J160"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" customWidth="1"/>
-    <col min="3" max="7" width="20" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>46049</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="3">
-        <v>89.91</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>46054</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3">
-        <v>89.91</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>46063</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="3">
-        <v>98.91</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>46067</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="3">
-        <v>38.25</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>46071</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3">
-        <v>33.56</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>46075</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3">
-        <v>20.7</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>46097</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="3">
-        <v>89.91</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>46099</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="3">
-        <v>89.91</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>46113</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="3">
-        <v>89.91</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="3">
-        <v>89.91</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>46135</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="3">
-        <v>89.91</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>46140</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="3">
-        <v>513</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>46151</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="3">
-        <v>170.9</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>46166</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="3">
-        <v>69.89</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46171</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="3">
-        <v>78.5</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>46174</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="3">
-        <v>30</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>46183</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="3">
-        <v>42.99</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>46193</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="3">
-        <v>415.1</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>46194</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="3">
-        <v>95</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>46203</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="3">
-        <v>359.64</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>46212</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="3">
-        <v>290.99</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>46230</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="3">
-        <v>50</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <v>46230</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="3">
-        <v>79.7</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>46239</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="3">
-        <v>92.05</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <v>46247</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="3">
-        <v>99.46</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>46252</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="3">
-        <v>197.8</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
-        <v>46253</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="3">
-        <v>269.73</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <v>46265</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="3">
-        <v>189.81</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
-        <v>46275</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="3">
-        <v>119.92</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <v>46275</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="3">
-        <v>114.79</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
-        <v>46275</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="3">
-        <v>179.82</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>46282</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="3"/>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="3"/>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="3"/>
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
-      <c r="G122" s="3"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
-      <c r="F123" s="3"/>
-      <c r="G123" s="3"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="3"/>
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
-      <c r="G124" s="3"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="3"/>
-      <c r="B125" s="3"/>
-      <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
-      <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
-      <c r="G125" s="3"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="3"/>
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
-      <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
-      <c r="G126" s="3"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
-      <c r="G127" s="3"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
-      <c r="E128" s="3"/>
-      <c r="F128" s="3"/>
-      <c r="G128" s="3"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
-      <c r="G129" s="3"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
-      <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
-      <c r="E130" s="3"/>
-      <c r="F130" s="3"/>
-      <c r="G130" s="3"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
-      <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
-      <c r="G131" s="3"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="3"/>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
-      <c r="D132" s="3"/>
-      <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
-      <c r="G132" s="3"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="3"/>
-      <c r="B133" s="3"/>
-      <c r="C133" s="3"/>
-      <c r="D133" s="3"/>
-      <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
-      <c r="G133" s="3"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="3"/>
-      <c r="B134" s="3"/>
-      <c r="C134" s="3"/>
-      <c r="D134" s="3"/>
-      <c r="E134" s="3"/>
-      <c r="F134" s="3"/>
-      <c r="G134" s="3"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="3"/>
-      <c r="B135" s="3"/>
-      <c r="C135" s="3"/>
-      <c r="D135" s="3"/>
-      <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
-      <c r="G135" s="3"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="3"/>
-      <c r="B136" s="3"/>
-      <c r="C136" s="3"/>
-      <c r="D136" s="3"/>
-      <c r="E136" s="3"/>
-      <c r="F136" s="3"/>
-      <c r="G136" s="3"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="3"/>
-      <c r="B137" s="3"/>
-      <c r="C137" s="3"/>
-      <c r="D137" s="3"/>
-      <c r="E137" s="3"/>
-      <c r="F137" s="3"/>
-      <c r="G137" s="3"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="3"/>
-      <c r="B138" s="3"/>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
-      <c r="E138" s="3"/>
-      <c r="F138" s="3"/>
-      <c r="G138" s="3"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="3"/>
-      <c r="B139" s="3"/>
-      <c r="C139" s="3"/>
-      <c r="D139" s="3"/>
-      <c r="E139" s="3"/>
-      <c r="F139" s="3"/>
-      <c r="G139" s="3"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="3"/>
-      <c r="B140" s="3"/>
-      <c r="C140" s="3"/>
-      <c r="D140" s="3"/>
-      <c r="E140" s="3"/>
-      <c r="F140" s="3"/>
-      <c r="G140" s="3"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="3"/>
-      <c r="B141" s="3"/>
-      <c r="C141" s="3"/>
-      <c r="D141" s="3"/>
-      <c r="E141" s="3"/>
-      <c r="F141" s="3"/>
-      <c r="G141" s="3"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
-      <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
-      <c r="F142" s="3"/>
-      <c r="G142" s="3"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
-      <c r="C143" s="3"/>
-      <c r="D143" s="3"/>
-      <c r="E143" s="3"/>
-      <c r="F143" s="3"/>
-      <c r="G143" s="3"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
-      <c r="C144" s="3"/>
-      <c r="D144" s="3"/>
-      <c r="E144" s="3"/>
-      <c r="F144" s="3"/>
-      <c r="G144" s="3"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
-      <c r="C145" s="3"/>
-      <c r="D145" s="3"/>
-      <c r="E145" s="3"/>
-      <c r="F145" s="3"/>
-      <c r="G145" s="3"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
-      <c r="F146" s="3"/>
-      <c r="G146" s="3"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
-      <c r="C147" s="3"/>
-      <c r="D147" s="3"/>
-      <c r="E147" s="3"/>
-      <c r="F147" s="3"/>
-      <c r="G147" s="3"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-      <c r="F148" s="3"/>
-      <c r="G148" s="3"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
-      <c r="C149" s="3"/>
-      <c r="D149" s="3"/>
-      <c r="E149" s="3"/>
-      <c r="F149" s="3"/>
-      <c r="G149" s="3"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
-      <c r="C150" s="3"/>
-      <c r="D150" s="3"/>
-      <c r="E150" s="3"/>
-      <c r="F150" s="3"/>
-      <c r="G150" s="3"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
-      <c r="C151" s="3"/>
-      <c r="D151" s="3"/>
-      <c r="E151" s="3"/>
-      <c r="F151" s="3"/>
-      <c r="G151" s="3"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
-      <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
-      <c r="E152" s="3"/>
-      <c r="F152" s="3"/>
-      <c r="G152" s="3"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="3"/>
-      <c r="B153" s="3"/>
-      <c r="C153" s="3"/>
-      <c r="D153" s="3"/>
-      <c r="E153" s="3"/>
-      <c r="F153" s="3"/>
-      <c r="G153" s="3"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="3"/>
-      <c r="B154" s="3"/>
-      <c r="C154" s="3"/>
-      <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
-      <c r="F154" s="3"/>
-      <c r="G154" s="3"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="3"/>
-      <c r="B155" s="3"/>
-      <c r="C155" s="3"/>
-      <c r="D155" s="3"/>
-      <c r="E155" s="3"/>
-      <c r="F155" s="3"/>
-      <c r="G155" s="3"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="3"/>
-      <c r="B156" s="3"/>
-      <c r="C156" s="3"/>
-      <c r="D156" s="3"/>
-      <c r="E156" s="3"/>
-      <c r="F156" s="3"/>
-      <c r="G156" s="3"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="3"/>
-      <c r="B157" s="3"/>
-      <c r="C157" s="3"/>
-      <c r="D157" s="3"/>
-      <c r="E157" s="3"/>
-      <c r="F157" s="3"/>
-      <c r="G157" s="3"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="3"/>
-      <c r="B158" s="3"/>
-      <c r="C158" s="3"/>
-      <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
-      <c r="F158" s="3"/>
-      <c r="G158" s="3"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="3"/>
-      <c r="B159" s="3"/>
-      <c r="C159" s="3"/>
-      <c r="D159" s="3"/>
-      <c r="E159" s="3"/>
-      <c r="F159" s="3"/>
-      <c r="G159" s="3"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-      <c r="F160" s="3"/>
-      <c r="G160" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2799,25 +820,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2825,10 +846,10 @@
         <v>46062</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3">
         <v>5</v>
@@ -2841,10 +862,10 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2852,10 +873,10 @@
         <v>46063</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -2868,10 +889,10 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2879,10 +900,10 @@
         <v>46073</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -2895,10 +916,10 @@
         <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2906,10 +927,10 @@
         <v>46073</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -2922,10 +943,10 @@
         <v>35</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2933,10 +954,10 @@
         <v>46119</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -2948,10 +969,10 @@
         <v>35</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2959,10 +980,10 @@
         <v>46120</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -2975,10 +996,10 @@
         <v>35</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2986,10 +1007,10 @@
         <v>46121</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -3002,10 +1023,10 @@
         <v>10</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3013,10 +1034,10 @@
         <v>46122</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -3029,10 +1050,10 @@
         <v>30</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3040,10 +1061,10 @@
         <v>46123</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -3056,10 +1077,10 @@
         <v>20</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3067,10 +1088,10 @@
         <v>46124</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -3083,10 +1104,10 @@
         <v>20</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3094,10 +1115,10 @@
         <v>46125</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3">
         <v>5</v>
@@ -3110,10 +1131,10 @@
         <v>50</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3121,10 +1142,10 @@
         <v>46126</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -3137,10 +1158,10 @@
         <v>10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3148,10 +1169,10 @@
         <v>46127</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3">
         <v>4</v>
@@ -3163,10 +1184,10 @@
         <v>37</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3174,10 +1195,10 @@
         <v>46128</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -3190,10 +1211,10 @@
         <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3201,10 +1222,10 @@
         <v>46129</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -3217,10 +1238,10 @@
         <v>25</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3228,10 +1249,10 @@
         <v>46130</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -3244,10 +1265,10 @@
         <v>35</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3255,10 +1276,10 @@
         <v>46131</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -3271,10 +1292,10 @@
         <v>15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3282,10 +1303,10 @@
         <v>46132</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D19" s="3">
         <v>10</v>
@@ -3297,10 +1318,10 @@
         <v>80</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3308,10 +1329,10 @@
         <v>46137</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D20" s="3">
         <v>2</v>
@@ -3324,10 +1345,10 @@
         <v>20</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3335,10 +1356,10 @@
         <v>46138</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
@@ -3351,10 +1372,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -3362,10 +1383,10 @@
         <v>46141</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -3378,10 +1399,10 @@
         <v>10</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -3389,10 +1410,10 @@
         <v>46148</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D23" s="3">
         <v>2</v>
@@ -3405,10 +1426,10 @@
         <v>80</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -3416,10 +1437,10 @@
         <v>46149</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D24" s="3">
         <v>10</v>
@@ -3432,10 +1453,10 @@
         <v>80</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -3443,10 +1464,10 @@
         <v>46149</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -3459,10 +1480,10 @@
         <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -3470,10 +1491,10 @@
         <v>46150</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D26" s="3">
         <v>1</v>
@@ -3486,10 +1507,10 @@
         <v>35</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3497,10 +1518,10 @@
         <v>46161</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D27" s="3">
         <v>18</v>
@@ -3513,10 +1534,10 @@
         <v>108</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -3524,10 +1545,10 @@
         <v>46161</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -3540,10 +1561,10 @@
         <v>10</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3551,10 +1572,10 @@
         <v>46161</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D29" s="3">
         <v>4</v>
@@ -3567,10 +1588,10 @@
         <v>32</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -3578,12 +1599,12 @@
         <v>46162</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="8">
+        <v>37</v>
+      </c>
+      <c r="D30" s="6">
         <v>1</v>
       </c>
       <c r="E30" s="3">
@@ -3594,10 +1615,10 @@
         <v>20</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -3605,10 +1626,10 @@
         <v>46163</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D31" s="3">
         <v>1</v>
@@ -3621,10 +1642,10 @@
         <v>35</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -3632,10 +1653,10 @@
         <v>46164</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -3648,10 +1669,10 @@
         <v>30</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -3659,10 +1680,10 @@
         <v>46168</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D33" s="3">
         <v>32</v>
@@ -3675,10 +1696,10 @@
         <v>192</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -3686,10 +1707,10 @@
         <v>46171</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
@@ -3702,10 +1723,10 @@
         <v>35</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -3713,10 +1734,10 @@
         <v>46171</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -3728,10 +1749,10 @@
         <v>10</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -3739,10 +1760,10 @@
         <v>46171</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -3755,10 +1776,10 @@
         <v>35</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -3766,10 +1787,10 @@
         <v>46174</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -3782,10 +1803,10 @@
         <v>35</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3793,10 +1814,10 @@
         <v>46174</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
@@ -3809,10 +1830,10 @@
         <v>206</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -3820,10 +1841,10 @@
         <v>46174</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D39" s="3">
         <v>1</v>
@@ -3836,10 +1857,10 @@
         <v>35</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -3847,10 +1868,10 @@
         <v>46175</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D40" s="3">
         <v>1</v>
@@ -3863,10 +1884,10 @@
         <v>40</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3874,10 +1895,10 @@
         <v>46176</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D41" s="3">
         <v>1</v>
@@ -3890,10 +1911,10 @@
         <v>45</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3901,10 +1922,10 @@
         <v>46179</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D42" s="3">
         <v>1</v>
@@ -3917,10 +1938,10 @@
         <v>30</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -3928,10 +1949,10 @@
         <v>46181</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D43" s="3">
         <v>20</v>
@@ -3944,10 +1965,10 @@
         <v>120</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3955,10 +1976,10 @@
         <v>46186</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D44" s="3">
         <v>30</v>
@@ -3971,10 +1992,10 @@
         <v>30</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -3982,10 +2003,10 @@
         <v>46186</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D45" s="3">
         <v>20</v>
@@ -3998,10 +2019,10 @@
         <v>20</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -4009,10 +2030,10 @@
         <v>46187</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D46" s="3">
         <v>10</v>
@@ -4025,10 +2046,10 @@
         <v>50</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -4036,10 +2057,10 @@
         <v>46188</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D47" s="3">
         <v>30</v>
@@ -4052,10 +2073,10 @@
         <v>60</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -4063,10 +2084,10 @@
         <v>46189</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -4079,10 +2100,10 @@
         <v>25</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -4090,10 +2111,10 @@
         <v>46187</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -4106,10 +2127,10 @@
         <v>170</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -4117,10 +2138,10 @@
         <v>46192</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D50" s="3">
         <v>2</v>
@@ -4133,10 +2154,10 @@
         <v>70</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -4144,10 +2165,10 @@
         <v>46192</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
@@ -4160,10 +2181,10 @@
         <v>20</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -4171,10 +2192,10 @@
         <v>46192</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
@@ -4187,10 +2208,10 @@
         <v>170</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -4198,10 +2219,10 @@
         <v>46199</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D53" s="3">
         <v>3</v>
@@ -4214,10 +2235,10 @@
         <v>45</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -4225,10 +2246,10 @@
         <v>46203</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D54" s="3">
         <v>10</v>
@@ -4241,10 +2262,10 @@
         <v>102</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4252,10 +2273,10 @@
         <v>46203</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D55" s="3">
         <v>40</v>
@@ -4268,10 +2289,10 @@
         <v>240</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -4279,10 +2300,10 @@
         <v>46204</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D56" s="3">
         <v>35</v>
@@ -4295,10 +2316,10 @@
         <v>35</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -4306,10 +2327,10 @@
         <v>46206</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D57" s="3">
         <v>30</v>
@@ -4322,10 +2343,10 @@
         <v>30</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4333,10 +2354,10 @@
         <v>46206</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D58" s="3">
         <v>35</v>
@@ -4349,10 +2370,10 @@
         <v>70</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4360,10 +2381,10 @@
         <v>46211</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D59" s="3">
         <v>40</v>
@@ -4376,10 +2397,10 @@
         <v>40</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4387,10 +2408,10 @@
         <v>46211</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D60" s="3">
         <v>110</v>
@@ -4403,10 +2424,10 @@
         <v>110</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4414,10 +2435,10 @@
         <v>46213</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D61" s="3">
         <v>35</v>
@@ -4430,10 +2451,10 @@
         <v>35</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -4441,10 +2462,10 @@
         <v>46213</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D62" s="3">
         <v>6</v>
@@ -4457,10 +2478,10 @@
         <v>240</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4468,10 +2489,10 @@
         <v>46229</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D63" s="3">
         <v>2</v>
@@ -4484,10 +2505,10 @@
         <v>70</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4495,10 +2516,10 @@
         <v>46229</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D64" s="3">
         <v>1</v>
@@ -4511,10 +2532,10 @@
         <v>50</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4522,10 +2543,10 @@
         <v>46229</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D65" s="3">
         <v>2</v>
@@ -4538,10 +2559,10 @@
         <v>50</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4549,10 +2570,10 @@
         <v>46230</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D66" s="3">
         <v>6</v>
@@ -4565,10 +2586,10 @@
         <v>240</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4576,10 +2597,10 @@
         <v>46239</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D67" s="3">
         <v>3</v>
@@ -4592,10 +2613,10 @@
         <v>75</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4603,10 +2624,10 @@
         <v>46240</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -4619,10 +2640,10 @@
         <v>50</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -4630,10 +2651,10 @@
         <v>46241</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -4646,10 +2667,10 @@
         <v>60</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -4657,10 +2678,10 @@
         <v>46245</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D70" s="3">
         <v>40</v>
@@ -4673,10 +2694,10 @@
         <v>240</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -4684,10 +2705,10 @@
         <v>46245</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D71" s="3">
         <v>30</v>
@@ -4700,10 +2721,10 @@
         <v>60</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -4711,10 +2732,10 @@
         <v>46248</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D72" s="3">
         <v>6</v>
@@ -4727,10 +2748,10 @@
         <v>240</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -4738,10 +2759,10 @@
         <v>46248</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D73" s="3">
         <v>18</v>
@@ -4754,10 +2775,10 @@
         <v>126</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -4765,10 +2786,10 @@
         <v>46263</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D74" s="3">
         <v>48</v>
@@ -4781,10 +2802,10 @@
         <v>384</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -4792,10 +2813,10 @@
         <v>46266</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D75" s="3">
         <v>50</v>
@@ -4808,10 +2829,10 @@
         <v>100</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -4819,10 +2840,10 @@
         <v>46273</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D76" s="3">
         <v>1</v>
@@ -4835,10 +2856,10 @@
         <v>396</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -4846,10 +2867,10 @@
         <v>46286</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D77" s="3">
         <v>1</v>
@@ -4862,10 +2883,10 @@
         <v>292</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -4873,10 +2894,10 @@
         <v>46287</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D78" s="3">
         <v>1</v>
@@ -4888,10 +2909,10 @@
         <v>35</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -4899,10 +2920,10 @@
         <v>46287</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D79" s="3">
         <v>2</v>
@@ -4915,10 +2936,10 @@
         <v>12</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -4926,10 +2947,10 @@
         <v>46294</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D80" s="3">
         <v>1</v>
@@ -4942,10 +2963,10 @@
         <v>20</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -4953,10 +2974,10 @@
         <v>46294</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D81" s="3">
         <v>1</v>
@@ -4969,10 +2990,10 @@
         <v>15</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -4980,10 +3001,10 @@
         <v>46295</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D82" s="3">
         <v>10</v>
@@ -4996,10 +3017,10 @@
         <v>100</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -5007,10 +3028,10 @@
         <v>46298</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D83" s="3">
         <v>42</v>
@@ -5023,10 +3044,10 @@
         <v>252</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -5034,10 +3055,10 @@
         <v>46298</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D84" s="3">
         <v>4</v>
@@ -5050,10 +3071,10 @@
         <v>72</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -5061,10 +3082,10 @@
         <v>46308</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D85" s="3">
         <v>48</v>
@@ -5077,10 +3098,10 @@
         <v>288</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -5088,10 +3109,10 @@
         <v>46308</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D86" s="3">
         <v>8</v>
@@ -5104,10 +3125,10 @@
         <v>144</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -5115,10 +3136,10 @@
         <v>46311</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
@@ -5131,10 +3152,10 @@
         <v>20</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -10640,9 +8661,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -10658,16 +8679,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10675,19 +8696,19 @@
         <v>46049</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -10695,19 +8716,19 @@
         <v>46054</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -10715,19 +8736,19 @@
         <v>46063</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -10735,19 +8756,19 @@
         <v>46067</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G5" s="3"/>
     </row>
@@ -10756,19 +8777,19 @@
         <v>46071</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -10777,19 +8798,19 @@
         <v>46075</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -10797,19 +8818,19 @@
         <v>46132</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -10817,19 +8838,19 @@
         <v>46133</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -10837,19 +8858,19 @@
         <v>46134</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -10857,19 +8878,19 @@
         <v>46135</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -10877,19 +8898,19 @@
         <v>46136</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -10897,19 +8918,19 @@
         <v>46137</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -10917,19 +8938,19 @@
         <v>46138</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -10937,19 +8958,19 @@
         <v>46151</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -10957,19 +8978,19 @@
         <v>46166</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G16" s="3"/>
     </row>
@@ -10978,19 +8999,19 @@
         <v>46171</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -10998,19 +9019,19 @@
         <v>46174</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -11018,19 +9039,19 @@
         <v>46183</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -11038,19 +9059,19 @@
         <v>46193</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -11058,19 +9079,19 @@
         <v>46194</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -11078,19 +9099,19 @@
         <v>46203</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -11098,19 +9119,19 @@
         <v>46210</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -11118,19 +9139,19 @@
         <v>46230</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -11138,19 +9159,19 @@
         <v>46230</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -11158,19 +9179,19 @@
         <v>46240</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -11178,19 +9199,19 @@
         <v>46247</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -11198,19 +9219,19 @@
         <v>46252</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -11218,19 +9239,19 @@
         <v>46253</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -11238,19 +9259,19 @@
         <v>46275</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -11258,19 +9279,19 @@
         <v>46275</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -11278,19 +9299,19 @@
         <v>46275</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -11298,19 +9319,39 @@
         <v>46282</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,22 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Vendas" sheetId="2" r:id="rId1"/>
     <sheet name="Gastos" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="141">
   <si>
     <t>Data</t>
   </si>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t>$176,34</t>
+  </si>
+  <si>
+    <t>$154,65</t>
   </si>
 </sst>
 </file>
@@ -8663,7 +8666,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -9354,6 +9357,26 @@
         <v>17</v>
       </c>
     </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>46318</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Vendas" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="141">
   <si>
     <t>Data</t>
   </si>
@@ -3162,10 +3162,30 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="3"/>
-      <c r="F88">
+      <c r="A88" s="4">
+        <v>46319</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D88" s="3">
+        <v>48</v>
+      </c>
+      <c r="E88" s="3">
+        <v>6</v>
+      </c>
+      <c r="F88" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>288</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
